--- a/Excel/DateFunctions1.xlsx
+++ b/Excel/DateFunctions1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98E297B-D71A-4929-A8DB-7C834F72A92E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090E9D75-CC03-4851-A5A0-338BC2FCC50F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="11200" activeTab="1" xr2:uid="{FAFC723F-6BF7-442A-9487-952B16EE793B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="11200" activeTab="6" xr2:uid="{FAFC723F-6BF7-442A-9487-952B16EE793B}"/>
   </bookViews>
   <sheets>
     <sheet name="Today" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Date" sheetId="3" r:id="rId3"/>
     <sheet name="DayMonthYear" sheetId="4" r:id="rId4"/>
     <sheet name="SerialNumber" sheetId="5" r:id="rId5"/>
+    <sheet name="EDate" sheetId="6" r:id="rId6"/>
+    <sheet name="DateDif" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>S.no</t>
   </si>
@@ -92,6 +94,51 @@
   </si>
   <si>
     <t>SerialNumber</t>
+  </si>
+  <si>
+    <t>OrderedDate</t>
+  </si>
+  <si>
+    <t>ExpectedDays</t>
+  </si>
+  <si>
+    <t>ActuallDeliveryDate</t>
+  </si>
+  <si>
+    <t>ExpectedMonths</t>
+  </si>
+  <si>
+    <t>ExpectedYears</t>
+  </si>
+  <si>
+    <t>PersonName</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>DatedifYear</t>
+  </si>
+  <si>
+    <t>DatedifMonth</t>
+  </si>
+  <si>
+    <t>DatedifDays</t>
+  </si>
+  <si>
+    <t>TodaysDate</t>
+  </si>
+  <si>
+    <t>ThiseYearBDate</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Days</t>
   </si>
 </sst>
 </file>
@@ -105,7 +152,7 @@
     <numFmt numFmtId="167" formatCode="[$-14009]d\.m\.yy;@"/>
     <numFmt numFmtId="168" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,16 +160,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -156,11 +235,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -205,6 +297,45 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,11 +688,11 @@
       </c>
       <c r="D2" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="E2" s="4">
         <f ca="1">D2-C2</f>
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -618,11 +749,11 @@
       </c>
       <c r="D2" s="7">
         <f ca="1">NOW()</f>
-        <v>46153.662011574073</v>
+        <v>46154.63814560185</v>
       </c>
       <c r="E2" s="10">
         <f ca="1">D2-C2</f>
-        <v>46153.287011574073</v>
+        <v>46154.26314560185</v>
       </c>
     </row>
   </sheetData>
@@ -818,30 +949,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B2" s="12">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C2" s="4">
         <f ca="1">YEAR(A2)</f>
@@ -853,7 +984,7 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">DAY(A2)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -895,10 +1026,10 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -948,16 +1079,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1005,4 +1136,910 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604B69C8-CF60-4753-AB45-9BFB54471CF5}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="B2" s="4">
+        <v>5</v>
+      </c>
+      <c r="C2" s="19">
+        <f ca="1">A2+B2</f>
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <f t="shared" ref="A3:A5" ca="1" si="0">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="B3" s="4">
+        <v>3</v>
+      </c>
+      <c r="C3" s="19">
+        <f t="shared" ref="C3:C5" ca="1" si="1">A3+B3</f>
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>46154</v>
+      </c>
+      <c r="B4" s="4">
+        <v>10</v>
+      </c>
+      <c r="C4" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>46154</v>
+      </c>
+      <c r="B5" s="4">
+        <v>7</v>
+      </c>
+      <c r="C5" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="B11" s="4">
+        <v>5</v>
+      </c>
+      <c r="C11" s="22">
+        <f ca="1">(B11 * 30) + A11</f>
+        <v>46304</v>
+      </c>
+      <c r="D11" s="21">
+        <f ca="1">EDATE(A11,B11)</f>
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <f t="shared" ref="A12:A14" ca="1" si="2">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3</v>
+      </c>
+      <c r="C12" s="22">
+        <f t="shared" ref="C12:C14" ca="1" si="3">(B12 * 30) + A12</f>
+        <v>46244</v>
+      </c>
+      <c r="D12" s="21">
+        <f t="shared" ref="D12:D14" ca="1" si="4">EDATE(A12,B12)</f>
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>46154</v>
+      </c>
+      <c r="B13" s="4">
+        <v>10</v>
+      </c>
+      <c r="C13" s="22">
+        <f t="shared" ca="1" si="3"/>
+        <v>46454</v>
+      </c>
+      <c r="D13" s="21">
+        <f t="shared" ca="1" si="4"/>
+        <v>46458</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>46154</v>
+      </c>
+      <c r="B14" s="4">
+        <v>7</v>
+      </c>
+      <c r="C14" s="22">
+        <f t="shared" ca="1" si="3"/>
+        <v>46364</v>
+      </c>
+      <c r="D14" s="21">
+        <f t="shared" ca="1" si="4"/>
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="B19" s="4">
+        <v>5</v>
+      </c>
+      <c r="C19" s="22">
+        <f ca="1" xml:space="preserve"> (B19 * 30 * 12 ) + A19</f>
+        <v>47954</v>
+      </c>
+      <c r="D19" s="21">
+        <f ca="1">EDATE(A19,B19*12)</f>
+        <v>47980</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="6">
+        <f t="shared" ref="A20:A22" ca="1" si="5">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3</v>
+      </c>
+      <c r="C20" s="22">
+        <f t="shared" ref="C20:C22" ca="1" si="6" xml:space="preserve"> (B20 * 30 * 12 ) + A20</f>
+        <v>47234</v>
+      </c>
+      <c r="D20" s="21">
+        <f t="shared" ref="D20:D22" ca="1" si="7">EDATE(A20,B20*12)</f>
+        <v>47250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>46154</v>
+      </c>
+      <c r="B21" s="4">
+        <v>100</v>
+      </c>
+      <c r="C21" s="22">
+        <f t="shared" ca="1" si="6"/>
+        <v>82154</v>
+      </c>
+      <c r="D21" s="21">
+        <f t="shared" ca="1" si="7"/>
+        <v>82678</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>46154</v>
+      </c>
+      <c r="B22" s="4">
+        <v>7</v>
+      </c>
+      <c r="C22" s="22">
+        <f t="shared" ca="1" si="6"/>
+        <v>48674</v>
+      </c>
+      <c r="D22" s="21">
+        <f t="shared" ca="1" si="7"/>
+        <v>48711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C682995-641E-413F-A8F8-844A213404E9}">
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="16.90625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.36328125" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6">
+        <v>35973</v>
+      </c>
+      <c r="C2" s="4">
+        <f ca="1">DATEDIF(B2,TODAY(),"Y")</f>
+        <v>27</v>
+      </c>
+      <c r="D2" s="5">
+        <f ca="1">DATEDIF(B2,TODAY(),"M")</f>
+        <v>334</v>
+      </c>
+      <c r="E2" s="4">
+        <f ca="1">DATEDIF(B2,TODAY(),"D")</f>
+        <v>10181</v>
+      </c>
+      <c r="G2" s="1">
+        <v>35927</v>
+      </c>
+      <c r="H2" s="4">
+        <f ca="1">DATEDIF(G2,TODAY(),"Y")</f>
+        <v>28</v>
+      </c>
+      <c r="I2" s="5">
+        <f ca="1">DATEDIF(G2,TODAY(),"M")</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6">
+        <v>38232</v>
+      </c>
+      <c r="C3" s="4">
+        <f t="shared" ref="C3:C7" ca="1" si="0">DATEDIF(B3,TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D3" s="5">
+        <f t="shared" ref="D3:D7" ca="1" si="1">DATEDIF(B3,TODAY(),"M")</f>
+        <v>260</v>
+      </c>
+      <c r="E3" s="4">
+        <f t="shared" ref="E3:E7" ca="1" si="2">DATEDIF(B3,TODAY(),"D")</f>
+        <v>7922</v>
+      </c>
+      <c r="I3" s="2">
+        <f>28 * 12</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="6">
+        <v>38237</v>
+      </c>
+      <c r="C4" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D4" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6">
+        <v>35411</v>
+      </c>
+      <c r="C5" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>353</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>10743</v>
+      </c>
+      <c r="G5" s="6">
+        <v>38232</v>
+      </c>
+      <c r="H5" s="1">
+        <f ca="1">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="I5" s="2">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6">
+        <v>34504</v>
+      </c>
+      <c r="C6" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="D6" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>382</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>11650</v>
+      </c>
+      <c r="I6" s="2">
+        <f>21 * 12</f>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="6">
+        <v>37126</v>
+      </c>
+      <c r="C7" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" ca="1" si="1"/>
+        <v>296</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>9028</v>
+      </c>
+      <c r="I7" s="20">
+        <f>I6+8</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6">
+        <v>35973</v>
+      </c>
+      <c r="C13" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="D13" s="5">
+        <f ca="1">DATEDIF(B13,C13,"Y")</f>
+        <v>27</v>
+      </c>
+      <c r="E13" s="4">
+        <f ca="1">DATEDIF(B13,C13,"M")</f>
+        <v>334</v>
+      </c>
+      <c r="F13" s="4">
+        <f ca="1">DATEDIF(B13,C13,"D")</f>
+        <v>10181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6">
+        <v>38232</v>
+      </c>
+      <c r="C14" s="6">
+        <f t="shared" ref="C14:C18" ca="1" si="3">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" ref="D14:D18" ca="1" si="4">DATEDIF(B14,C14,"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" ref="E14:E18" ca="1" si="5">DATEDIF(B14,C14,"M")</f>
+        <v>260</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" ref="F14:F18" ca="1" si="6">DATEDIF(B14,C14,"D")</f>
+        <v>7922</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6">
+        <v>38237</v>
+      </c>
+      <c r="C15" s="6">
+        <f t="shared" ca="1" si="3"/>
+        <v>46154</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" ca="1" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" ca="1" si="5"/>
+        <v>260</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" ca="1" si="6"/>
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6">
+        <v>35411</v>
+      </c>
+      <c r="C16" s="6">
+        <f t="shared" ca="1" si="3"/>
+        <v>46154</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" ca="1" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" ca="1" si="5"/>
+        <v>353</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" ca="1" si="6"/>
+        <v>10743</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6">
+        <v>34504</v>
+      </c>
+      <c r="C17" s="6">
+        <f t="shared" ca="1" si="3"/>
+        <v>46154</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" ca="1" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" ca="1" si="5"/>
+        <v>382</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" ca="1" si="6"/>
+        <v>11650</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6">
+        <v>37126</v>
+      </c>
+      <c r="C18" s="6">
+        <f t="shared" ca="1" si="3"/>
+        <v>46154</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" ca="1" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" ca="1" si="5"/>
+        <v>296</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" ca="1" si="6"/>
+        <v>9028</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="6">
+        <v>35973</v>
+      </c>
+      <c r="C23" s="6">
+        <v>46200</v>
+      </c>
+      <c r="D23" s="5">
+        <f>DATEDIF(B23,C23,"Y")</f>
+        <v>28</v>
+      </c>
+      <c r="E23" s="4">
+        <f>DATEDIF(B23,C23,"M")</f>
+        <v>336</v>
+      </c>
+      <c r="F23" s="4">
+        <f>DATEDIF(B23,C23,"D")</f>
+        <v>10227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="6">
+        <v>38232</v>
+      </c>
+      <c r="C24" s="6">
+        <v>46267</v>
+      </c>
+      <c r="D24" s="5">
+        <f t="shared" ref="D24:D28" si="7">DATEDIF(B24,C24,"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" ref="E24:E28" si="8">DATEDIF(B24,C24,"M")</f>
+        <v>264</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" ref="F24:F28" si="9">DATEDIF(B24,C24,"D")</f>
+        <v>8035</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="6">
+        <v>38237</v>
+      </c>
+      <c r="C25" s="6">
+        <v>46272</v>
+      </c>
+      <c r="D25" s="5">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="E25" s="4">
+        <f t="shared" si="8"/>
+        <v>264</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" si="9"/>
+        <v>8035</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="6">
+        <v>35411</v>
+      </c>
+      <c r="C26" s="6">
+        <v>46368</v>
+      </c>
+      <c r="D26" s="5">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="8"/>
+        <v>360</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="9"/>
+        <v>10957</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="6">
+        <v>34504</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46192</v>
+      </c>
+      <c r="D27" s="5">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="8"/>
+        <v>384</v>
+      </c>
+      <c r="F27" s="4">
+        <f>DATEDIF(B27,C27,"D")</f>
+        <v>11688</v>
+      </c>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="6">
+        <v>37126</v>
+      </c>
+      <c r="C28" s="6">
+        <v>46257</v>
+      </c>
+      <c r="D28" s="5">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="8"/>
+        <v>300</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="9"/>
+        <v>9131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="25"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="6">
+        <v>35973</v>
+      </c>
+      <c r="C34" s="4">
+        <f ca="1">DATEDIF(B34,TODAY(),"Y")</f>
+        <v>27</v>
+      </c>
+      <c r="D34" s="28">
+        <f ca="1">DATEDIF(B34,TODAY(),"YM")</f>
+        <v>10</v>
+      </c>
+      <c r="E34" s="4">
+        <f ca="1">DATEDIF(B34,TODAY(),"MD")</f>
+        <v>15</v>
+      </c>
+      <c r="F34" s="25"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="6">
+        <v>38232</v>
+      </c>
+      <c r="C35" s="4">
+        <f t="shared" ref="C35:C39" ca="1" si="10">DATEDIF(B35,TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D35" s="28">
+        <f t="shared" ref="D35:D39" ca="1" si="11">DATEDIF(B35,TODAY(),"YM")</f>
+        <v>8</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" ref="E35:E39" ca="1" si="12">DATEDIF(B35,TODAY(),"MD")</f>
+        <v>10</v>
+      </c>
+      <c r="F35" s="25"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="6">
+        <v>38237</v>
+      </c>
+      <c r="C36" s="4">
+        <f t="shared" ca="1" si="10"/>
+        <v>21</v>
+      </c>
+      <c r="D36" s="28">
+        <f t="shared" ca="1" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ca="1" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F36" s="25"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="6">
+        <v>35411</v>
+      </c>
+      <c r="C37" s="4">
+        <f ca="1">DATEDIF(B37,TODAY(),"Y")</f>
+        <v>29</v>
+      </c>
+      <c r="D37" s="28">
+        <f t="shared" ca="1" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="25"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="24">
+        <v>34504</v>
+      </c>
+      <c r="C38" s="23">
+        <f t="shared" ca="1" si="10"/>
+        <v>31</v>
+      </c>
+      <c r="D38" s="29">
+        <f t="shared" ca="1" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" ca="1" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="F38" s="26"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="6">
+        <v>37126</v>
+      </c>
+      <c r="C39" s="4">
+        <f t="shared" ca="1" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="D39" s="28">
+        <f t="shared" ca="1" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" ca="1" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="F39" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Excel/DateFunctions1.xlsx
+++ b/Excel/DateFunctions1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090E9D75-CC03-4851-A5A0-338BC2FCC50F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DA722A-190B-45FB-B995-D50261F9203F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="11200" activeTab="6" xr2:uid="{FAFC723F-6BF7-442A-9487-952B16EE793B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="11200" firstSheet="6" activeTab="6" xr2:uid="{FAFC723F-6BF7-442A-9487-952B16EE793B}"/>
   </bookViews>
   <sheets>
     <sheet name="Today" sheetId="1" r:id="rId1"/>
@@ -749,11 +749,11 @@
       </c>
       <c r="D2" s="7">
         <f ca="1">NOW()</f>
-        <v>46154.63814560185</v>
+        <v>46154.660750000003</v>
       </c>
       <c r="E2" s="10">
         <f ca="1">D2-C2</f>
-        <v>46154.26314560185</v>
+        <v>46154.285750000003</v>
       </c>
     </row>
   </sheetData>
